--- a/docs/saenggibu-form-extra.xlsx
+++ b/docs/saenggibu-form-extra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yeungnam\Desktop\2026학년도\교무기획부\학교생활기록부\보조자료\서식\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yeungnam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAECF4B7-507C-46BF-923C-83AAA1B25B60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17651403-3544-48E2-AB78-5B5CD4F1B5D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="12930" xr2:uid="{E640C6C8-5B7B-4838-AB41-FC15DA4BDA2F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="15135" xr2:uid="{E640C6C8-5B7B-4838-AB41-FC15DA4BDA2F}"/>
   </bookViews>
   <sheets>
     <sheet name="부서○○(활동명○○)" sheetId="1" r:id="rId1"/>
@@ -28,13 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>⊙ 활  동  명:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>학생회 임원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -66,153 +62,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>직책</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>기재 내용</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>○○○○부</t>
@@ -269,12 +120,20 @@
     <t>자율활동 특기사항 or 진로활동 특기사항</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>자기평가서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>진로탐색 로봇공학캠프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,13 +189,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -768,7 +620,7 @@
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="5" width="5.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="52.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="72.625" style="1" customWidth="1"/>
     <col min="9" max="26" width="9" style="1"/>
     <col min="27" max="28" width="9" style="1" hidden="1" customWidth="1"/>
@@ -777,7 +629,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -786,7 +638,7 @@
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="10" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H1" s="10"/>
     </row>
@@ -795,18 +647,18 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="10" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="H2" s="10"/>
       <c r="AA2" s="1" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -814,7 +666,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="str">
@@ -823,42 +675,42 @@
       </c>
       <c r="H3" s="13"/>
       <c r="AA3" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="AA4" s="1" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" ht="60" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <f>C5&amp;TEXT(D5,"00")&amp;TEXT(E5,"00")</f>
         <v>0000</v>
@@ -875,13 +727,13 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="AA5" s="1" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" ht="60" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <f t="shared" ref="A6:A69" si="0">C6&amp;TEXT(D6,"00")&amp;TEXT(E6,"00")</f>
         <v>30115</v>
@@ -898,13 +750,13 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="AA6" s="1" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="72" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30118</v>
@@ -921,13 +773,13 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="AA7" s="1" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="48" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30124</v>
@@ -944,7 +796,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:28" ht="84" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30133</v>
@@ -961,7 +813,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:28" ht="84" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30323</v>
@@ -978,7 +830,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:28" ht="60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>30406</v>
@@ -995,7 +847,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:28" ht="60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>31508</v>
@@ -1012,7 +864,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:28" ht="48" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20122</v>
@@ -1029,7 +881,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:28" ht="48" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20207</v>
@@ -1046,7 +898,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:28" ht="48" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20221</v>
@@ -1063,7 +915,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:28" ht="48" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20325</v>
@@ -1080,7 +932,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" ht="48" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20711</v>
@@ -1097,7 +949,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" ht="48" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>20714</v>
@@ -1114,7 +966,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" ht="48" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>21118</v>
@@ -1131,7 +983,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>11301</v>
@@ -10179,7 +10031,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="B4:H4" xr:uid="{EEDC6316-EB99-466E-AB5A-6D335D3426D7}">
     <sortState ref="B5:H20">
       <sortCondition descending="1" ref="C4"/>

--- a/docs/saenggibu-form-extra.xlsx
+++ b/docs/saenggibu-form-extra.xlsx
@@ -736,7 +736,7 @@
     <row r="6" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <f t="shared" ref="A6:A69" si="0">C6&amp;TEXT(D6,"00")&amp;TEXT(E6,"00")</f>
-        <v>30115</v>
+        <v>0000</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -759,7 +759,7 @@
     <row r="7" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>30118</v>
+        <v>0000</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -782,7 +782,7 @@
     <row r="8" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>30124</v>
+        <v>0000</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -799,7 +799,7 @@
     <row r="9" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>30133</v>
+        <v>0000</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -816,7 +816,7 @@
     <row r="10" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>30323</v>
+        <v>0000</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -833,7 +833,7 @@
     <row r="11" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>30406</v>
+        <v>0000</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -850,7 +850,7 @@
     <row r="12" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>31508</v>
+        <v>0000</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -867,7 +867,7 @@
     <row r="13" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>20122</v>
+        <v>0000</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -884,7 +884,7 @@
     <row r="14" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>20207</v>
+        <v>0000</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -901,7 +901,7 @@
     <row r="15" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>20221</v>
+        <v>0000</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -918,7 +918,7 @@
     <row r="16" spans="1:28" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>20325</v>
+        <v>0000</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -935,7 +935,7 @@
     <row r="17" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>20711</v>
+        <v>0000</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -952,7 +952,7 @@
     <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>20714</v>
+        <v>0000</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -969,7 +969,7 @@
     <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>21118</v>
+        <v>0000</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -986,7 +986,7 @@
     <row r="20" spans="1:12" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>11301</v>
+        <v>0000</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
